--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486873_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486873_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0486</v>
+        <v>4.6865</v>
       </c>
       <c r="E2" t="n">
-        <v>2.114</v>
+        <v>1.5523</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9345</v>
+        <v>3.1342</v>
       </c>
       <c r="G2" t="n">
         <v>4.9624</v>
@@ -610,13 +610,13 @@
         <v>0.4107</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5696</v>
+        <v>2.2075</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3248</v>
+        <v>0.763</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2448</v>
+        <v>1.4445</v>
       </c>
       <c r="V2" t="n">
         <v>2.2394</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0785</v>
+        <v>4.5731</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1258</v>
+        <v>3.5375</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9527</v>
+        <v>1.0355</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5172</v>
+        <v>4.6073</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2647</v>
+        <v>0.8366</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2526</v>
+        <v>3.7707</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1265</v>
+        <v>4.2273</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7583</v>
+        <v>1.1095</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6318</v>
+        <v>3.1178</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3907</v>
+        <v>0.38</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4937</v>
+        <v>-0.2729</v>
       </c>
       <c r="O3" t="n">
-        <v>1.8844</v>
+        <v>0.6529</v>
       </c>
       <c r="P3" t="n">
         <v>-0.616</v>
@@ -688,28 +688,28 @@
         <v>0.4107</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9371</v>
+        <v>0.5773</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5456</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3916</v>
+        <v>0.4806</v>
       </c>
       <c r="V3" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="W3" t="n">
         <v>0.2402</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.4805</v>
-      </c>
       <c r="X3" t="n">
-        <v>-0.2402</v>
+        <v>-0.2357</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0748</v>
+        <v>4.1856</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1579</v>
+        <v>1.9365</v>
       </c>
       <c r="F4" t="n">
-        <v>0.917</v>
+        <v>2.2491</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6073</v>
+        <v>3.5172</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8366</v>
+        <v>2.2647</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7707</v>
+        <v>1.2526</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2273</v>
+        <v>2.1265</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1095</v>
+        <v>2.7583</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1178</v>
+        <v>-0.6318</v>
       </c>
       <c r="M4" t="n">
-        <v>0.38</v>
+        <v>1.3907</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2729</v>
+        <v>-0.4937</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6529</v>
+        <v>1.8844</v>
       </c>
       <c r="P4" t="n">
         <v>-0.616</v>
@@ -766,28 +766,28 @@
         <v>0.4107</v>
       </c>
       <c r="S4" t="n">
-        <v>0.079</v>
+        <v>1.0442</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.283</v>
+        <v>0.3562</v>
       </c>
       <c r="U4" t="n">
-        <v>0.362</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0045</v>
+        <v>0.2402</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2402</v>
+        <v>0.4805</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2357</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>J. GOLSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1673</v>
+        <v>3.1176</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3131</v>
+        <v>2.5997</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4804</v>
+        <v>0.5179</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6027</v>
+        <v>3.8906</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3917</v>
+        <v>-0.782</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9944</v>
+        <v>4.6727</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9345</v>
+        <v>4.1689</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3947</v>
+        <v>0.0779</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4602</v>
+        <v>4.091</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5372</v>
+        <v>-0.2783</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003</v>
+        <v>-0.8599</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5342</v>
+        <v>0.5816</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.4374</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6448</v>
+        <v>0.6073</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3176</v>
+        <v>0.244</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3272</v>
+        <v>0.3633</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3573</v>
+        <v>-0.3536</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3573</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GOLSON</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9694</v>
+        <v>2.6181</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5997</v>
+        <v>-0.4177</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3697</v>
+        <v>3.0358</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8906</v>
+        <v>0.6027</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.782</v>
+        <v>-1.3917</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6727</v>
+        <v>1.9944</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1689</v>
+        <v>-0.9345</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0779</v>
+        <v>-1.3947</v>
       </c>
       <c r="L6" t="n">
-        <v>4.091</v>
+        <v>0.4602</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2783</v>
+        <v>1.5372</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8599</v>
+        <v>0.003</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5816</v>
+        <v>1.5342</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0267</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4591</v>
+        <v>1.0955</v>
       </c>
       <c r="T6" t="n">
-        <v>0.244</v>
+        <v>0.213</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2151</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3536</v>
+        <v>2.3573</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2402</v>
+        <v>2.3573</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. VILA I GÓMEZ</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5293</v>
+        <v>0.5812</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-1.0441</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5293</v>
+        <v>1.6253</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4184</v>
+        <v>-1.537</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-1.9397</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4184</v>
+        <v>0.4027</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-2.0327</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-1.3879</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.6449</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4184</v>
+        <v>0.4957</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4184</v>
+        <v>1.0476</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.4107</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.4107</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1108</v>
+        <v>0.5289</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1108</v>
+        <v>0.7189</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CARRASCO MARTIN</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.265</v>
+        <v>0.5359</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5537</v>
+        <v>-0.9408</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8187</v>
+        <v>1.4767</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6857</v>
+        <v>0.3161</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2488</v>
+        <v>0.1134</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4368</v>
+        <v>0.2027</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5929</v>
+        <v>-0.6579</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1324</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5395</v>
+        <v>-0.6579</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0927</v>
+        <v>0.974</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1164</v>
+        <v>0.1134</v>
       </c>
       <c r="O8" t="n">
-        <v>1.9763</v>
+        <v>0.8606</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.2588</v>
+        <v>0.4107</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0213</v>
+        <v>-0.1908</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6933</v>
+        <v>-0.2829</v>
       </c>
       <c r="U8" t="n">
-        <v>0.328</v>
+        <v>0.0921</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1831</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>A. VILA I GÓMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1646</v>
+        <v>0.4107</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0454</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.21</v>
+        <v>0.4107</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3161</v>
+        <v>0.4184</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1134</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2027</v>
+        <v>0.4184</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6579</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6579</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.974</v>
+        <v>0.4184</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1134</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8606</v>
+        <v>0.4184</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5622</v>
+        <v>-0.0077</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3875</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1747</v>
+        <v>-0.0077</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.143</v>
+        <v>0.2301</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8724</v>
+        <v>-1.5586</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7294</v>
+        <v>1.7887</v>
       </c>
       <c r="G10" t="n">
         <v>0.4116</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6733</v>
+        <v>-0.3002</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1172</v>
+        <v>0.1765</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7027</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>J. CARRASCO MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2103</v>
+        <v>-0.0143</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7763</v>
+        <v>-2.0108</v>
       </c>
       <c r="F11" t="n">
-        <v>1.566</v>
+        <v>1.9965</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.537</v>
+        <v>2.6857</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9397</v>
+        <v>1.2488</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4027</v>
+        <v>1.4368</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0327</v>
+        <v>0.5929</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3879</v>
+        <v>1.1324</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6449</v>
+        <v>-0.5395</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4957</v>
+        <v>2.0927</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.1164</v>
       </c>
       <c r="O11" t="n">
-        <v>1.0476</v>
+        <v>1.9763</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4107</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2626</v>
+        <v>0.742</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9222</v>
+        <v>0.2361</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6596</v>
+        <v>0.5058</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1786</v>
+        <v>-1.1831</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.4234</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2271</v>
+        <v>-1.878</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5323</v>
+        <v>-4.4204</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3052</v>
+        <v>2.5424</v>
       </c>
       <c r="G12" t="n">
         <v>-4.8628</v>
@@ -1390,13 +1390,13 @@
         <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6206</v>
+        <v>0.7285</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.2787</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2126</v>
+        <v>0.4497</v>
       </c>
       <c r="V12" t="n">
         <v>2.4616</v>
@@ -1423,43 +1423,43 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.7171</v>
+        <v>19.0465</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0958</v>
+        <v>-0.7663999999999986</v>
       </c>
       <c r="F13" t="n">
-        <v>19.8129</v>
+        <v>19.8128</v>
       </c>
       <c r="G13" t="n">
         <v>15.0122</v>
       </c>
       <c r="H13" t="n">
-        <v>1.540199999999999</v>
+        <v>1.5402</v>
       </c>
       <c r="I13" t="n">
         <v>13.4721</v>
       </c>
       <c r="J13" t="n">
-        <v>4.162099999999999</v>
+        <v>4.162100000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>4.414900000000001</v>
+        <v>4.4149</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2527999999999997</v>
+        <v>-0.2528000000000006</v>
       </c>
       <c r="M13" t="n">
         <v>10.85</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.8747</v>
+        <v>-2.874699999999999</v>
       </c>
       <c r="O13" t="n">
         <v>13.7248</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.240299999999998</v>
+        <v>-9.2403</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.4006</v>
@@ -1468,16 +1468,16 @@
         <v>6.160399999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>6.702999999999999</v>
+        <v>7.0325</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9089000000000006</v>
+        <v>1.2381</v>
       </c>
       <c r="U13" t="n">
-        <v>5.794200000000001</v>
+        <v>5.7943</v>
       </c>
       <c r="V13" t="n">
-        <v>6.2422</v>
+        <v>6.242199999999999</v>
       </c>
       <c r="W13" t="n">
         <v>9.2338</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>M. GARCIA ROSELLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0468</v>
+        <v>2.0645</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6856</v>
+        <v>2.5583</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3612</v>
+        <v>-0.4939</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9781</v>
+        <v>2.8085</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9594</v>
+        <v>0.2011</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9813</v>
+        <v>2.6074</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1009</v>
+        <v>3.0078</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4561</v>
+        <v>0.5874</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3552</v>
+        <v>2.4204</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1227</v>
+        <v>-0.1993</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4967</v>
+        <v>-0.3863</v>
       </c>
       <c r="O14" t="n">
-        <v>0.374</v>
+        <v>0.187</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2588</v>
+        <v>1.0267</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2588</v>
+        <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2242</v>
+        <v>-0.3564</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5847</v>
+        <v>-0.4495</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3605</v>
+        <v>0.0931</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4144</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GARCIA ROSELLO</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9738</v>
+        <v>1.7728</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3491</v>
+        <v>-0.1791</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3753</v>
+        <v>1.9519</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8085</v>
+        <v>0.842</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2011</v>
+        <v>0.0419</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6074</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0078</v>
+        <v>0.5724</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5874</v>
+        <v>0.7042</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4204</v>
+        <v>-0.1318</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1993</v>
+        <v>0.2696</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3863</v>
+        <v>-0.6623</v>
       </c>
       <c r="O15" t="n">
-        <v>0.187</v>
+        <v>0.9318</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0267</v>
+        <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.447</v>
+        <v>-1.1004</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6587</v>
+        <v>-0.5543</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2117</v>
+        <v>-0.5461</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4144</v>
+        <v>0.5938</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.8295</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4144</v>
+        <v>-0.2357</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9401</v>
+        <v>1.7033</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7623</v>
+        <v>0.9534</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1777</v>
+        <v>0.7499</v>
       </c>
       <c r="G16" t="n">
-        <v>0.842</v>
+        <v>0.9781</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0419</v>
+        <v>1.9594</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>-0.9813</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5724</v>
+        <v>1.1009</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7042</v>
+        <v>2.4561</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1318</v>
+        <v>-1.3552</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2696</v>
+        <v>-0.1227</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6623</v>
+        <v>-0.4967</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9318</v>
+        <v>0.374</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4374</v>
+        <v>2.2588</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4641</v>
+        <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9331</v>
+        <v>-0.1192</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3871</v>
+        <v>-0.1475</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3202</v>
+        <v>0.0283</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5938</v>
+        <v>-1.4144</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2357</v>
+        <v>-1.4144</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1587</v>
+        <v>1.0845</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0099</v>
+        <v>-1.5915</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1686</v>
+        <v>2.676</v>
       </c>
       <c r="G17" t="n">
         <v>-0.393</v>
@@ -1780,13 +1780,13 @@
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1259</v>
+        <v>-1.2001</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3756</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7503</v>
+        <v>-0.243</v>
       </c>
       <c r="V17" t="n">
         <v>0.8295</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1386</v>
+        <v>0.1822</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3601</v>
+        <v>1.2555</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2215</v>
+        <v>-1.0733</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1693</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0679</v>
+        <v>-0.0243</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3566</v>
+        <v>-0.4612</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2887</v>
+        <v>0.4369</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2402</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1519</v>
+        <v>-1.0743</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7275</v>
+        <v>0.3091</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-1.3834</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2769</v>
@@ -1936,13 +1936,13 @@
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0937</v>
+        <v>0.1714</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0114</v>
+        <v>-0.407</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0823</v>
+        <v>0.5784</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1741</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6692</v>
+        <v>-1.8757</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2967</v>
+        <v>-3.3168</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3726</v>
+        <v>1.4411</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5424</v>
+        <v>-1.3333</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4152</v>
+        <v>0.1296</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.9576</v>
+        <v>-1.4629</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.835</v>
+        <v>-1.3524</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9149</v>
+        <v>0.0423</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.7499</v>
+        <v>-1.3947</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7074</v>
+        <v>0.0191</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4997</v>
+        <v>0.0873</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2077</v>
+        <v>-0.0682</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6677999999999999</v>
+        <v>-0.9182</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5384</v>
+        <v>-0.9378</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1295</v>
+        <v>0.0195</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3499</v>
+        <v>-2.2829</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6306</v>
+        <v>-2.0289</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2807</v>
+        <v>-0.254</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3333</v>
+        <v>-2.5424</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1296</v>
+        <v>0.4152</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4629</v>
+        <v>-2.9576</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3524</v>
+        <v>-1.835</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0423</v>
+        <v>0.9149</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3947</v>
+        <v>-2.7499</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0191</v>
+        <v>-0.7074</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0873</v>
+        <v>-0.4997</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0682</v>
+        <v>-0.2077</v>
       </c>
       <c r="P21" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3924</v>
+        <v>0.0542</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2516</v>
+        <v>-0.1939</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1409</v>
+        <v>0.248</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1737</v>
+        <v>-2.3073</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3527</v>
+        <v>-3.9343</v>
       </c>
       <c r="F22" t="n">
-        <v>1.179</v>
+        <v>1.627</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2594</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3518</v>
+        <v>-0.4853</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1198</v>
+        <v>-0.7014</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2319</v>
+        <v>0.2161</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4048</v>
+        <v>-2.5645</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0968</v>
+        <v>-3.5738</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.0093</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6326</v>
@@ -2248,13 +2248,13 @@
         <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1562</v>
+        <v>-0.3158</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7169</v>
+        <v>-0.1939</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4393</v>
+        <v>-0.122</v>
       </c>
       <c r="V23" t="n">
         <v>0.5893</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3853</v>
+        <v>-5.2197</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8506</v>
+        <v>-2.5367</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5348</v>
+        <v>-2.683</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7123</v>
@@ -2326,13 +2326,13 @@
         <v>0.2053</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0407</v>
+        <v>0.1249</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7498</v>
+        <v>0.6016</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8377</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.84</v>
+        <v>-8.107799999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.460100000000001</v>
+        <v>-7.7279</v>
       </c>
       <c r="F25" t="n">
         <v>-0.3799</v>
@@ -2404,10 +2404,10 @@
         <v>1.6427</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1739</v>
+        <v>-0.4417</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0462</v>
+        <v>-0.314</v>
       </c>
       <c r="U25" t="n">
         <v>-0.1277</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.7168</v>
+        <v>-16.6249</v>
       </c>
       <c r="E26" t="n">
-        <v>-19.8128</v>
+        <v>-19.8127</v>
       </c>
       <c r="F26" t="n">
-        <v>1.095600000000001</v>
+        <v>3.1877</v>
       </c>
       <c r="G26" t="n">
         <v>-15.0122</v>
@@ -2458,7 +2458,7 @@
         <v>-10.8498</v>
       </c>
       <c r="K26" t="n">
-        <v>2.874800000000001</v>
+        <v>2.8748</v>
       </c>
       <c r="L26" t="n">
         <v>-13.7249</v>
@@ -2470,7 +2470,7 @@
         <v>-4.415</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2527000000000001</v>
+        <v>0.2527000000000006</v>
       </c>
       <c r="P26" t="n">
         <v>9.2403</v>
@@ -2482,13 +2482,13 @@
         <v>15.4006</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.7032</v>
+        <v>-4.6109</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.794299999999999</v>
+        <v>-5.7944</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9088000000000002</v>
+        <v>1.1831</v>
       </c>
       <c r="V26" t="n">
         <v>-6.2423</v>
